--- a/data/trans_dic/IP07_R2-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP07_R2-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4,78%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6,53%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6,06%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>5,17%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>5,03%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>8,56%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>13,56%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,78%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,53%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 12,15</t>
+          <t>0,0; 8,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,45; 12,68</t>
+          <t>1,46; 11,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,71; 16,97</t>
+          <t>2,72; 13,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,42; 36,09</t>
+          <t>2,57; 12,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,27</t>
+          <t>1,3; 11,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,45; 11,61</t>
+          <t>1,06; 11,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,17; 13,5</t>
+          <t>3,66; 16,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,29; 12,51</t>
+          <t>3,44; 16,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,26; 7,47</t>
+          <t>1,24; 7,6</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,3; 9,46</t>
+          <t>2,18; 9,18</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4,03; 12,74</t>
+          <t>4,46; 12,53</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,58; 23,22</t>
+          <t>3,77; 11,94</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>4,14%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4,18%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3,38%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>1,81%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>3,1%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2,26%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,81%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,14%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,18%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>3,38%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,91</t>
+          <t>1,8; 8,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,22; 6,88</t>
+          <t>1,74; 8,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 6,73</t>
+          <t>1,19; 7,12</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 6,69</t>
+          <t>0,36; 5,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,81; 8,37</t>
+          <t>0,57; 4,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,77; 8,32</t>
+          <t>1,21; 6,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 8,05</t>
+          <t>0,56; 6,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 4,96</t>
+          <t>1,24; 8,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,5; 5,15</t>
+          <t>1,51; 5,32</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,09; 6,22</t>
+          <t>2,07; 6,08</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 5,31</t>
+          <t>1,32; 5,48</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,39</t>
+          <t>1,22; 5,28</t>
         </is>
       </c>
     </row>
@@ -929,62 +929,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1,17%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1,08%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2,64%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2,27%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,84</t>
+          <t>0,86; 7,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,75</t>
+          <t>0,0; 5,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,37 +1012,37 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 8,08</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 5,87</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 6,52</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,86; 6,73</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,55</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,47</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,69</t>
+          <t>0,46; 4,75</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,56</t>
+          <t>0,0; 3,64</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,28</t>
+          <t>0,0; 4,17</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,31%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3,48%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3,68%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>4,2%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,08%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1,06; 8,65</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 4,75</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0,97; 8,85</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 12,01</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1,08; 8,71</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1,5; 9,45</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1,12; 10,95</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,86; 8,7</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,5</t>
+          <t>1,04; 9,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 8,14</t>
+          <t>1,5; 9,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,28</t>
+          <t>1,15; 10,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,49</t>
+          <t>0,44; 4,48</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 5,3</t>
+          <t>0,98; 5,46</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,8; 6,83</t>
+          <t>1,78; 6,83</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 7,52</t>
+          <t>0,79; 7,79</t>
         </is>
       </c>
     </row>
@@ -1209,62 +1209,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>7,76%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7,15%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>4,69%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>7,76%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>7,15%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>6,28%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>3,69%</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>6,28%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -1277,34 +1277,34 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 13,7</t>
+          <t>3,08; 17,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>2,79; 14,64</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 7,53</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,47; 12,51</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,93</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3,07; 17,02</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,73; 14,58</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1312,17 +1312,17 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,85</t>
+          <t>0,0; 7,4</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,45; 12,47</t>
+          <t>3,05; 11,4</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,46; 8,56</t>
+          <t>1,45; 7,96</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,67</t>
+          <t>0,0; 5,2</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>1,14%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1,3%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>1,15%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,31</t>
+          <t>0,0; 6,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,74</t>
+          <t>0,0; 5,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,28</t>
+          <t>0,0; 7,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,46</t>
+          <t>0,52; 9,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,43</t>
+          <t>0,0; 6,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,83</t>
+          <t>0,0; 6,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,92</t>
+          <t>0,0; 6,41</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,14</t>
+          <t>0,0; 8,88</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,39</t>
+          <t>0,53; 4,72</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,29</t>
+          <t>0,0; 4,32</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,39</t>
+          <t>0,0; 4,23</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,66; 5,87</t>
+          <t>0,67; 5,96</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2,51%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3,83%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>1,04%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1,43%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>0,96%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,51%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,14</t>
+          <t>0,99; 6,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,84</t>
+          <t>0,44; 4,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,02</t>
+          <t>0,47; 4,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 5,67</t>
+          <t>1,76; 7,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,58</t>
+          <t>0,0; 3,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,45; 4,5</t>
+          <t>0,47; 3,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,35</t>
+          <t>0,0; 3,24</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,54; 7,22</t>
+          <t>0,56; 6,01</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,58</t>
+          <t>0,76; 3,35</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,19</t>
+          <t>0,68; 3,27</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,12</t>
+          <t>0,48; 2,87</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,52; 5,32</t>
+          <t>1,61; 5,45</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>4,15%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>1,49%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>2,58%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>0,65%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>4,15%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,59</t>
+          <t>2,1; 7,48</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,17; 5,86</t>
+          <t>0,46; 4,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,26</t>
+          <t>0,0; 2,45</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,67</t>
+          <t>0,0; 3,58</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,07; 7,07</t>
+          <t>0,4; 3,46</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,39; 4,37</t>
+          <t>1,22; 5,87</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,36</t>
+          <t>0,0; 1,96</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,23</t>
+          <t>0,0; 3,72</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,42</t>
+          <t>1,61; 4,56</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,62</t>
+          <t>1,05; 3,57</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,64</t>
+          <t>0,18; 1,8</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,12</t>
+          <t>0,0; 2,04</t>
         </is>
       </c>
     </row>
@@ -1769,62 +1769,62 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>3,53%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>1,71%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>2,34%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>1,91%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2,0%</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>2,5%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,74</t>
+          <t>2,57; 4,9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,42</t>
+          <t>1,67; 3,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,05</t>
+          <t>1,29; 3,12</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,93; 6,63</t>
+          <t>1,54; 3,61</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,5; 4,7</t>
+          <t>1,01; 2,74</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,75; 3,51</t>
+          <t>1,53; 3,49</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,27; 3,08</t>
+          <t>1,21; 2,97</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,62</t>
+          <t>1,58; 3,83</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1,97; 3,35</t>
+          <t>2,04; 3,4</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,21</t>
+          <t>1,85; 3,16</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,66</t>
+          <t>1,49; 2,62</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,36</t>
+          <t>1,85; 3,3</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1383</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>3024</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4168</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3890</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>2718</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>2854</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>4845</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>9937</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1383</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>3024</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>4168</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4547</t>
+          <t>4681</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14484</t>
+          <t>8571</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>710; 6388</t>
+          <t>0; 4783</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>819; 7191</t>
+          <t>926; 7275</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2102; 9604</t>
+          <t>1739; 8898</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3237; 26450</t>
+          <t>1651; 8206</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4912</t>
+          <t>684; 6147</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>915; 7352</t>
+          <t>599; 6503</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1387; 8618</t>
+          <t>2073; 9557</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1817; 9929</t>
+          <t>1944; 9419</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1412; 8366</t>
+          <t>1391; 8507</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2765; 11352</t>
+          <t>2613; 11015</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4849; 15349</t>
+          <t>5371; 15098</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6992; 35451</t>
+          <t>4548; 14406</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4472</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4648</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3733</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1957</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1840</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3242</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2338</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3591</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4472</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4648</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3733</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2211</t>
+          <t>3654</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5802</t>
+          <t>5611</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>580; 4986</t>
+          <t>1942; 8752</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1279; 7204</t>
+          <t>1934; 9115</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>570; 6954</t>
+          <t>1310; 7853</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>961; 8544</t>
+          <t>413; 6182</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1960; 9044</t>
+          <t>580; 4978</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1965; 9249</t>
+          <t>1267; 7184</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1376; 8880</t>
+          <t>579; 6787</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>518; 6329</t>
+          <t>1260; 8534</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3152; 10804</t>
+          <t>3167; 11144</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4521; 13429</t>
+          <t>4462; 13129</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2757; 11343</t>
+          <t>2814; 11696</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2507; 11210</t>
+          <t>2642; 11478</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,62 +2557,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1854</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1378</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>791</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>731</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1854</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2645</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1378</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1527</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>2645</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>1378</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>1527</t>
         </is>
       </c>
     </row>
@@ -2625,12 +2625,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3944</t>
+          <t>607; 4945</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3876</t>
+          <t>0; 3533</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2640,37 +2640,37 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
+          <t>0; 4801</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3965</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4393</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>606; 4731</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3208</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>0; 5015</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>618; 6464</t>
+          <t>633; 6558</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 4906</t>
+          <t>0; 5016</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 5368</t>
+          <t>0; 4836</t>
         </is>
       </c>
     </row>
@@ -2697,42 +2697,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,49 +2765,49 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2770</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2823</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1506</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2859</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>3231</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2860</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2950</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>2770</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1062</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2823</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1463</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2770</t>
-        </is>
-      </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
           <t>3921</t>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4323</t>
+          <t>4456</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>842; 6841</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3836</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>785; 7181</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 8668</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>841; 6774</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>1156; 7273</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>786; 7681</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>678; 6886</t>
-        </is>
-      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3635</t>
+          <t>811; 7119</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>698; 6605</t>
+          <t>1158; 7110</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 7254</t>
+          <t>815; 7581</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>678; 6915</t>
+          <t>683; 6892</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1543; 8409</t>
+          <t>1558; 8662</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2850; 10806</t>
+          <t>2821; 10808</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1124; 11157</t>
+          <t>1129; 11138</t>
         </is>
       </c>
     </row>
@@ -2905,32 +2905,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2973,62 +2973,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>3481</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3341</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>1963</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>3481</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>5444</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>3341</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>5444</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>3341</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1148</t>
+          <t>1091</t>
         </is>
       </c>
     </row>
@@ -3041,34 +3041,34 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>617; 5734</t>
+          <t>1382; 7654</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>1305; 6843</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2979</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>614; 5237</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>0; 2736</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>1378; 7634</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>1276; 6819</t>
-        </is>
-      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -3076,17 +3076,17 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 2791</t>
+          <t>0; 2635</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2127; 10814</t>
+          <t>2646; 9887</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1324; 7763</t>
+          <t>1312; 7212</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 3513</t>
+          <t>0; 3912</t>
         </is>
       </c>
     </row>
@@ -3113,42 +3113,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1274</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1475</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>640</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>726</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>608</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>668</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1274</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>790</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>635</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2338</t>
+          <t>2110</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 2977</t>
+          <t>0; 3904</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4333</t>
+          <t>0; 3547</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3854</t>
+          <t>0; 4036</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 3446</t>
+          <t>257; 4569</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 4436</t>
+          <t>0; 3681</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 3511</t>
+          <t>0; 3706</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 5012</t>
+          <t>0; 3392</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 5138</t>
+          <t>0; 4063</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>611; 5087</t>
+          <t>612; 5467</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 4990</t>
+          <t>0; 5018</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 4794</t>
+          <t>0; 4620</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>678; 6010</t>
+          <t>633; 5648</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>3378</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2566</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2705</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>5416</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>1333</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>1967</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>1316</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>2693</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>3378</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>2566</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>2705</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>5745</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>8438</t>
+          <t>8181</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4041</t>
+          <t>1331; 8078</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>642; 5296</t>
+          <t>642; 6485</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 4149</t>
+          <t>676; 6696</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>773; 7059</t>
+          <t>2492; 11007</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1355; 7495</t>
+          <t>0; 4605</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>656; 6556</t>
+          <t>645; 5316</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>685; 6238</t>
+          <t>0; 4445</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>2397; 11257</t>
+          <t>690; 7358</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2035; 9415</t>
+          <t>2000; 8798</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1929; 9053</t>
+          <t>1933; 9274</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1573; 8748</t>
+          <t>1350; 8069</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4270; 14925</t>
+          <t>4253; 14390</t>
         </is>
       </c>
     </row>
@@ -3529,32 +3529,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>6800</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1280</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>938</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>2360</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>4242</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>1060</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>848</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>6800</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>2750</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1280</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>936</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1753</t>
+          <t>1873</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>638; 5671</t>
+          <t>3440; 12279</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1925; 9657</t>
+          <t>786; 7132</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 3710</t>
+          <t>0; 4183</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 4832</t>
+          <t>0; 5702</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3394; 11598</t>
+          <t>636; 5471</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>671; 7481</t>
+          <t>2001; 9669</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0; 4031</t>
+          <t>0; 3213</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 5071</t>
+          <t>0; 5223</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5317; 14224</t>
+          <t>5185; 14670</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3521; 12162</t>
+          <t>3520; 11982</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>586; 5495</t>
+          <t>587; 6034</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0; 6129</t>
+          <t>0; 6108</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>25414</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>18726</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>15499</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>17131</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>11645</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>16619</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>13398</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>21144</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>25414</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>18726</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>15499</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>18669</t>
+          <t>16140</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>39813</t>
+          <t>33271</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>7265; 18649</t>
+          <t>18490; 35297</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>10563; 24280</t>
+          <t>12486; 26716</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>8737; 21336</t>
+          <t>9584; 23187</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12880; 44185</t>
+          <t>10764; 25332</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>18030; 33821</t>
+          <t>6868; 18628</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13095; 26308</t>
+          <t>10857; 24748</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9417; 22821</t>
+          <t>8496; 20805</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>11965; 27555</t>
+          <t>9944; 24126</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>27533; 46954</t>
+          <t>28607; 47605</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>26198; 46783</t>
+          <t>27038; 46163</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>20921; 38333</t>
+          <t>21541; 37817</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>28069; 62247</t>
+          <t>24678; 43909</t>
         </is>
       </c>
     </row>
